--- a/artfynd/A 35410-2026 artfynd.xlsx
+++ b/artfynd/A 35410-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194055</v>
       </c>
       <c r="B2" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194056</v>
       </c>
       <c r="B3" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194079</v>
       </c>
       <c r="B4" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136194080</v>
       </c>
       <c r="B5" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136194081</v>
       </c>
       <c r="B6" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136194082</v>
       </c>
       <c r="B7" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136194083</v>
       </c>
       <c r="B8" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136194084</v>
       </c>
       <c r="B9" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136194085</v>
       </c>
       <c r="B10" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35410-2026 artfynd.xlsx
+++ b/artfynd/A 35410-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194055</v>
       </c>
       <c r="B2" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194056</v>
       </c>
       <c r="B3" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194079</v>
       </c>
       <c r="B4" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136194080</v>
       </c>
       <c r="B5" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136194081</v>
       </c>
       <c r="B6" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136194082</v>
       </c>
       <c r="B7" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136194083</v>
       </c>
       <c r="B8" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136194084</v>
       </c>
       <c r="B9" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136194085</v>
       </c>
       <c r="B10" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35410-2026 artfynd.xlsx
+++ b/artfynd/A 35410-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194055</v>
       </c>
       <c r="B2" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194056</v>
       </c>
       <c r="B3" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194079</v>
       </c>
       <c r="B4" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136194080</v>
       </c>
       <c r="B5" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136194081</v>
       </c>
       <c r="B6" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136194082</v>
       </c>
       <c r="B7" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136194083</v>
       </c>
       <c r="B8" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136194084</v>
       </c>
       <c r="B9" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136194085</v>
       </c>
       <c r="B10" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35410-2026 artfynd.xlsx
+++ b/artfynd/A 35410-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194055</v>
       </c>
       <c r="B2" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194056</v>
       </c>
       <c r="B3" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194079</v>
       </c>
       <c r="B4" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136194080</v>
       </c>
       <c r="B5" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136194081</v>
       </c>
       <c r="B6" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136194082</v>
       </c>
       <c r="B7" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136194083</v>
       </c>
       <c r="B8" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136194084</v>
       </c>
       <c r="B9" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136194085</v>
       </c>
       <c r="B10" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35410-2026 artfynd.xlsx
+++ b/artfynd/A 35410-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194055</v>
       </c>
       <c r="B2" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194056</v>
       </c>
       <c r="B3" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194079</v>
       </c>
       <c r="B4" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136194080</v>
       </c>
       <c r="B5" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136194081</v>
       </c>
       <c r="B6" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136194082</v>
       </c>
       <c r="B7" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136194083</v>
       </c>
       <c r="B8" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136194084</v>
       </c>
       <c r="B9" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136194085</v>
       </c>
       <c r="B10" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35410-2026 artfynd.xlsx
+++ b/artfynd/A 35410-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194055</v>
       </c>
       <c r="B2" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194056</v>
       </c>
       <c r="B3" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194079</v>
       </c>
       <c r="B4" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136194080</v>
       </c>
       <c r="B5" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136194081</v>
       </c>
       <c r="B6" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136194082</v>
       </c>
       <c r="B7" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136194083</v>
       </c>
       <c r="B8" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136194084</v>
       </c>
       <c r="B9" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136194085</v>
       </c>
       <c r="B10" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35410-2026 artfynd.xlsx
+++ b/artfynd/A 35410-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194055</v>
       </c>
       <c r="B2" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194056</v>
       </c>
       <c r="B3" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194079</v>
       </c>
       <c r="B4" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136194080</v>
       </c>
       <c r="B5" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136194081</v>
       </c>
       <c r="B6" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136194082</v>
       </c>
       <c r="B7" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136194083</v>
       </c>
       <c r="B8" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136194084</v>
       </c>
       <c r="B9" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136194085</v>
       </c>
       <c r="B10" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35410-2026 artfynd.xlsx
+++ b/artfynd/A 35410-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194055</v>
       </c>
       <c r="B2" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194056</v>
       </c>
       <c r="B3" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194079</v>
       </c>
       <c r="B4" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136194080</v>
       </c>
       <c r="B5" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136194081</v>
       </c>
       <c r="B6" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136194082</v>
       </c>
       <c r="B7" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136194083</v>
       </c>
       <c r="B8" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136194084</v>
       </c>
       <c r="B9" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136194085</v>
       </c>
       <c r="B10" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35410-2026 artfynd.xlsx
+++ b/artfynd/A 35410-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194055</v>
       </c>
       <c r="B2" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136194056</v>
       </c>
       <c r="B3" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136194079</v>
       </c>
       <c r="B4" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136194080</v>
       </c>
       <c r="B5" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136194081</v>
       </c>
       <c r="B6" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136194082</v>
       </c>
       <c r="B7" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136194083</v>
       </c>
       <c r="B8" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136194084</v>
       </c>
       <c r="B9" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136194085</v>
       </c>
       <c r="B10" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
